--- a/output/roomself_excel/11756.xlsx
+++ b/output/roomself_excel/11756.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>193952</v>
+        <v>88945</v>
       </c>
       <c r="D2" t="n">
-        <v>3612</v>
+        <v>2460</v>
       </c>
       <c r="E2" t="n">
-        <v>665</v>
+        <v>355</v>
       </c>
       <c r="F2" t="n">
-        <v>590</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>104762</v>
+        <v>193952</v>
       </c>
       <c r="D3" t="n">
-        <v>3716</v>
+        <v>3612</v>
       </c>
       <c r="E3" t="n">
-        <v>665</v>
+        <v>590</v>
       </c>
       <c r="F3" t="n">
-        <v>309</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88945</v>
+        <v>95348</v>
       </c>
       <c r="D5" t="n">
-        <v>2460</v>
+        <v>2544</v>
       </c>
       <c r="E5" t="n">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95348</v>
+        <v>25066</v>
       </c>
       <c r="D6" t="n">
-        <v>2544</v>
+        <v>1268</v>
       </c>
       <c r="E6" t="n">
-        <v>433</v>
+        <v>151</v>
       </c>
       <c r="F6" t="n">
-        <v>281</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25066</v>
+        <v>74818</v>
       </c>
       <c r="D7" t="n">
-        <v>1268</v>
+        <v>2928</v>
       </c>
       <c r="E7" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>29944</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1396</v>
+      </c>
+      <c r="E8" t="n">
+        <v>152</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11756.xlsx
+++ b/output/roomself_excel/11756.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2460</v>
       </c>
-      <c r="E2" t="n">
-        <v>355</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>260</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>300</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3612</v>
       </c>
-      <c r="E3" t="n">
-        <v>590</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>370</v>
+        <v>551</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>352</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2808</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>355</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>18</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>347</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2544</v>
       </c>
-      <c r="E5" t="n">
-        <v>433</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>281</v>
+        <v>242</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>394</v>
+      </c>
+      <c r="J5" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>1268</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>151</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>27</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>2928</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>145</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>27</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1396</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>152</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>18</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/11756.xlsx
+++ b/output/roomself_excel/11756.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +537,22 @@
       <c r="J2" t="n">
         <v>27</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>122</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +591,22 @@
       <c r="J3" t="n">
         <v>39</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>210</v>
+      </c>
+      <c r="N3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +645,22 @@
       <c r="J4" t="n">
         <v>39</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>211</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,6 +699,22 @@
       <c r="J5" t="n">
         <v>39</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>216</v>
+      </c>
+      <c r="N5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +745,10 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +779,22 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>90</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -721,6 +825,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
